--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/MANGUEIRA FLEXIVEL FREIO 11_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/MANGUEIRA FLEXIVEL FREIO 11_02.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>602883767553</t>
+          <t> </t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/MANGUEIRA FLEXIVEL FREIO 11_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/MANGUEIRA FLEXIVEL FREIO 11_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,7 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -553,7 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,7 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -595,11 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -620,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -645,11 +612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -670,7 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -691,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -716,24 +672,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
